--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU01/HRM/post DFS_HRM-2031-0112/Panel-28/coupon_back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU01_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.89628</v>
+        <v>16.72742</v>
       </c>
       <c r="D2" t="n">
-        <v>16.56686</v>
+        <v>16.57198</v>
       </c>
       <c r="E2" t="n">
-        <v>16.77233</v>
+        <v>16.68359</v>
       </c>
       <c r="F2" t="n">
-        <v>41.74223</v>
+        <v>42.39406</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05033</v>
+        <v>0.04882</v>
       </c>
       <c r="H2" t="n">
-        <v>1.80423</v>
+        <v>1.78743</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.82602</v>
+        <v>16.67954</v>
       </c>
       <c r="D3" t="n">
-        <v>16.16018</v>
+        <v>16.44488</v>
       </c>
       <c r="E3" t="n">
-        <v>16.21625</v>
+        <v>16.66428</v>
       </c>
       <c r="F3" t="n">
-        <v>42.74042</v>
+        <v>42.28102</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05178</v>
+        <v>0.0496</v>
       </c>
       <c r="H3" t="n">
-        <v>1.80981</v>
+        <v>1.80214</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.39463</v>
+        <v>16.80988</v>
       </c>
       <c r="D4" t="n">
-        <v>16.57133</v>
+        <v>16.53466</v>
       </c>
       <c r="E4" t="n">
-        <v>16.58476</v>
+        <v>16.78175</v>
       </c>
       <c r="F4" t="n">
-        <v>42.54918</v>
+        <v>41.92537</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04999</v>
+        <v>0.04976</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8108</v>
+        <v>1.81676</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.85755</v>
+        <v>16.48638</v>
       </c>
       <c r="D6" t="n">
-        <v>15.99895</v>
+        <v>16.06807</v>
       </c>
       <c r="E6" t="n">
-        <v>16.41535</v>
+        <v>16.19217</v>
       </c>
       <c r="F6" t="n">
-        <v>21.346</v>
+        <v>21.51533</v>
       </c>
       <c r="G6" t="n">
-        <v>33.95793</v>
+        <v>33.93721</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.71944</v>
+        <v>16.62006</v>
       </c>
       <c r="D7" t="n">
-        <v>15.68447</v>
+        <v>15.85891</v>
       </c>
       <c r="E7" t="n">
-        <v>16.21115</v>
+        <v>15.96186</v>
       </c>
       <c r="F7" t="n">
-        <v>21.80785</v>
+        <v>20.84791</v>
       </c>
       <c r="G7" t="n">
-        <v>33.41186</v>
+        <v>33.5033</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.34867</v>
+        <v>16.88171</v>
       </c>
       <c r="D8" t="n">
-        <v>15.81943</v>
+        <v>15.53805</v>
       </c>
       <c r="E8" t="n">
-        <v>16.42496</v>
+        <v>16.10095</v>
       </c>
       <c r="F8" t="n">
-        <v>21.09086</v>
+        <v>21.4971</v>
       </c>
       <c r="G8" t="n">
-        <v>34.63358</v>
+        <v>33.64284</v>
       </c>
     </row>
   </sheetData>
